--- a/Tablets 25-26.xlsx
+++ b/Tablets 25-26.xlsx
@@ -1,31 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matiasmoschen/Library/CloudStorage/GoogleDrive-matias@amh.com.ar/Otros ordenadores/PC G. DRIVE/Downloads/reporte_agdp_v2/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BCB8663-5D6E-C842-92BC-2DDC32FE1E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12580"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Socios" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>Contratista</t>
   </si>
@@ -36,136 +26,163 @@
     <t>Villa Marcelo</t>
   </si>
   <si>
+    <t>1VILLA</t>
+  </si>
+  <si>
+    <t>2VILLA</t>
+  </si>
+  <si>
+    <t>3VILLA</t>
+  </si>
+  <si>
+    <t>4VILLA</t>
+  </si>
+  <si>
     <t>Amh</t>
   </si>
   <si>
+    <t>5AMH</t>
+  </si>
+  <si>
+    <t>6AMH</t>
+  </si>
+  <si>
+    <t>7AMH</t>
+  </si>
+  <si>
     <t>Maggi Javier</t>
   </si>
   <si>
+    <t>8MAGGI</t>
+  </si>
+  <si>
+    <t>9MAGGI</t>
+  </si>
+  <si>
+    <t>10MAGGI</t>
+  </si>
+  <si>
+    <t>11MAGGI</t>
+  </si>
+  <si>
     <t>Torrente Jose</t>
   </si>
   <si>
+    <t>12TORRENTE</t>
+  </si>
+  <si>
+    <t>13TORRENTE</t>
+  </si>
+  <si>
     <t>Dorchs Emilio</t>
   </si>
   <si>
+    <t>14DORCHS</t>
+  </si>
+  <si>
+    <t>15DORCHS</t>
+  </si>
+  <si>
     <t>Niemics Conrrado</t>
   </si>
   <si>
+    <t>16NIEMIC</t>
+  </si>
+  <si>
+    <t>17NIEMIC</t>
+  </si>
+  <si>
     <t>Gerardo Moschen</t>
   </si>
   <si>
+    <t>18GERARDO</t>
+  </si>
+  <si>
+    <t>19GERARDO</t>
+  </si>
+  <si>
+    <t>20GERARDO</t>
+  </si>
+  <si>
+    <t>21GERARDO</t>
+  </si>
+  <si>
     <t>Lamy Dario</t>
   </si>
   <si>
+    <t>22LAMY</t>
+  </si>
+  <si>
+    <t>27LAMY</t>
+  </si>
+  <si>
     <t>Colussi Gustavo</t>
   </si>
   <si>
+    <t>23GCOLUSSI5</t>
+  </si>
+  <si>
+    <t>28GCOLUSSI5</t>
+  </si>
+  <si>
     <t>Constantini Leandro</t>
   </si>
   <si>
-    <t>8MAGGI</t>
-  </si>
-  <si>
     <t>24CONSTANTINI</t>
   </si>
   <si>
-    <t>1VILLA</t>
-  </si>
-  <si>
-    <t>2VILLA</t>
-  </si>
-  <si>
-    <t>3VILLA</t>
-  </si>
-  <si>
-    <t>4VILLA</t>
-  </si>
-  <si>
-    <t>22LAMY</t>
-  </si>
-  <si>
-    <t>5AMH</t>
-  </si>
-  <si>
-    <t>6AMH</t>
-  </si>
-  <si>
-    <t>9MAGGI</t>
-  </si>
-  <si>
-    <t>16NIEMIC</t>
-  </si>
-  <si>
-    <t>17NIEMIC</t>
-  </si>
-  <si>
-    <t>12TORRENTE</t>
-  </si>
-  <si>
-    <t>13TORRENTE</t>
-  </si>
-  <si>
-    <t>14DORCHS</t>
-  </si>
-  <si>
-    <t>15DORCHS</t>
-  </si>
-  <si>
-    <t>10MAGGI</t>
-  </si>
-  <si>
-    <t>11MAGGI</t>
-  </si>
-  <si>
-    <t>7AMH</t>
-  </si>
-  <si>
-    <t>18GERARDO</t>
-  </si>
-  <si>
-    <t>19GERARDO</t>
-  </si>
-  <si>
-    <t>20GERARDO</t>
-  </si>
-  <si>
-    <t>21GERARDO</t>
-  </si>
-  <si>
-    <t>27LAMY</t>
-  </si>
-  <si>
-    <t>23GCOLUSSI5</t>
-  </si>
-  <si>
     <t>25CONSTANTINI</t>
   </si>
   <si>
     <t>26CONSTANTINI</t>
   </si>
   <si>
-    <t>28GCOLUSSI5</t>
+    <t>Socio</t>
+  </si>
+  <si>
+    <t>G&amp;M Agronegocios</t>
+  </si>
+  <si>
+    <t>ProvInvest</t>
+  </si>
+  <si>
+    <t>Zunesma</t>
+  </si>
+  <si>
+    <t>Romaju</t>
+  </si>
+  <si>
+    <t>Fermanelli</t>
+  </si>
+  <si>
+    <t>Meraki</t>
+  </si>
+  <si>
+    <t>Otros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -177,7 +194,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,17 +226,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,248 +517,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="23.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1" t="s">
+    <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1" t="s">
+    <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1" t="s">
+    <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/Tablets 25-26.xlsx
+++ b/Tablets 25-26.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
   <si>
     <t>Contratista</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Otros</t>
+  </si>
+  <si>
+    <t>Ganagro</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -811,8 +814,13 @@
         <v>47</v>
       </c>
     </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>